--- a/src/main/resources/static/diplomaformato.xlsx
+++ b/src/main/resources/static/diplomaformato.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="116">
   <si>
     <t xml:space="preserve">N°</t>
   </si>
@@ -188,10 +188,13 @@
     <t xml:space="preserve">observación</t>
   </si>
   <si>
-    <t xml:space="preserve">Aistencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profesot</t>
+    <t xml:space="preserve">asisntecia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">correo</t>
   </si>
   <si>
     <t xml:space="preserve">MARCELO ESCALONA NEIRA</t>
@@ -218,6 +221,9 @@
     <t xml:space="preserve">Marcelo Tapia A.</t>
   </si>
   <si>
+    <t xml:space="preserve">javierulloafierro@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALEXIS STOBER ALARCÓN</t>
   </si>
   <si>
@@ -288,6 +294,9 @@
   </si>
   <si>
     <t xml:space="preserve">CLAUDIA BARRALES Y TAMARA ELSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fierrovergararosaelizabeth@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">FRANCISCA GONZÁLEZ AVILÉS</t>
@@ -381,6 +390,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -403,18 +413,21 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -422,17 +435,20 @@
       <color rgb="FF000000"/>
       <name val="Verdana"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Verdana"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -538,7 +554,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -558,160 +574,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="16" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Excel Built-in Comma [0]" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -890,356 +902,356 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="10.95703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="57.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="57.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.49"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1262,150 +1274,150 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.95703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="57.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="57.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.49"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="49" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="49" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="49" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+    <row r="4" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="49" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="5" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="49" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+    <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1428,170 +1440,170 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="10.95703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="57.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="57.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.49"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="10"/>
+      <c r="H2" s="11"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+    <row r="7" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1614,170 +1626,170 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="10.95703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="65.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="65.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.49"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="10"/>
+      <c r="H2" s="11"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1797,20 +1809,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultColWidth="10.95703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="15.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
         <v>47</v>
       </c>
@@ -1847,39 +1859,45 @@
       <c r="L1" s="18" t="s">
         <v>55</v>
       </c>
+      <c r="M1" s="0" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2" s="13"/>
-      <c r="G2" s="0" t="s">
-        <v>60</v>
+      <c r="G2" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I2" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J2" s="13"/>
-      <c r="K2" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>63</v>
+      <c r="K2" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,373 +1905,406 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>63</v>
+      <c r="M3" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="13"/>
+      <c r="G4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="13"/>
+      <c r="K4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="0" t="s">
         <v>65</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>66</v>
+      <c r="B5" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F5" s="13"/>
-      <c r="G5" s="0" t="s">
-        <v>60</v>
+      <c r="G5" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I5" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J5" s="13"/>
-      <c r="K5" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>63</v>
+      <c r="K5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>67</v>
+      <c r="B6" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="13"/>
-      <c r="G6" s="0" t="s">
-        <v>60</v>
+      <c r="G6" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I6" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J6" s="13"/>
-      <c r="K6" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="0" t="s">
-        <v>63</v>
+      <c r="K6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>68</v>
+      <c r="B7" s="21" t="s">
+        <v>70</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F7" s="13"/>
-      <c r="G7" s="0" t="s">
-        <v>60</v>
+      <c r="G7" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I7" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J7" s="13"/>
-      <c r="K7" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>63</v>
+      <c r="K7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
+      <c r="B8" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="13"/>
-      <c r="G8" s="0" t="s">
-        <v>60</v>
+      <c r="G8" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I8" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J8" s="13"/>
-      <c r="K8" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>63</v>
+      <c r="K8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>70</v>
+      <c r="B9" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" s="13"/>
-      <c r="G9" s="0" t="s">
-        <v>60</v>
+      <c r="G9" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I9" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J9" s="13"/>
-      <c r="K9" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>63</v>
+      <c r="K9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>71</v>
+      <c r="B10" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" s="13"/>
-      <c r="G10" s="0" t="s">
-        <v>60</v>
+      <c r="G10" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I10" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J10" s="13"/>
-      <c r="K10" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>63</v>
+      <c r="K10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>72</v>
+      <c r="B11" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="13"/>
-      <c r="G11" s="0" t="s">
-        <v>60</v>
+      <c r="G11" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I11" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J11" s="13"/>
-      <c r="K11" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>63</v>
+      <c r="K11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>73</v>
+      <c r="B12" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="13"/>
-      <c r="G12" s="0" t="s">
-        <v>60</v>
+      <c r="G12" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I12" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J12" s="13"/>
-      <c r="K12" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>63</v>
+      <c r="K12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>74</v>
+      <c r="B13" s="21" t="s">
+        <v>76</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="13"/>
-      <c r="G13" s="0" t="s">
-        <v>60</v>
+      <c r="G13" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I13" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J13" s="13"/>
-      <c r="K13" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>63</v>
+      <c r="K13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2261,33 +2312,36 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="13"/>
-      <c r="G14" s="0" t="s">
-        <v>60</v>
+      <c r="G14" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I14" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J14" s="13"/>
-      <c r="K14" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>63</v>
+      <c r="K14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2295,33 +2349,36 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="13"/>
-      <c r="G15" s="0" t="s">
-        <v>60</v>
+      <c r="G15" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I15" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J15" s="13"/>
-      <c r="K15" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>63</v>
+      <c r="K15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2329,33 +2386,36 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" s="13"/>
-      <c r="G16" s="0" t="s">
-        <v>60</v>
+      <c r="G16" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I16" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I16" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J16" s="13"/>
-      <c r="K16" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="0" t="s">
-        <v>63</v>
+      <c r="K16" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2363,33 +2423,36 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" s="13"/>
-      <c r="G17" s="0" t="s">
-        <v>60</v>
+      <c r="G17" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I17" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J17" s="13"/>
-      <c r="K17" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="0" t="s">
-        <v>63</v>
+      <c r="K17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2397,33 +2460,36 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="13"/>
-      <c r="G18" s="0" t="s">
-        <v>60</v>
+      <c r="G18" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I18" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I18" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J18" s="13"/>
-      <c r="K18" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>63</v>
+      <c r="K18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2431,33 +2497,36 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" s="13"/>
-      <c r="G19" s="0" t="s">
-        <v>60</v>
+      <c r="G19" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I19" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I19" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J19" s="13"/>
-      <c r="K19" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="0" t="s">
-        <v>63</v>
+      <c r="K19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2465,67 +2534,73 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="D21" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I20" s="20" t="s">
+      <c r="E21" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J20" s="13"/>
-      <c r="K20" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="0" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="n">
+      <c r="I21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="13"/>
-      <c r="K21" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L21" s="0" t="s">
-        <v>63</v>
+      <c r="L21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2533,33 +2608,36 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" s="13"/>
-      <c r="G22" s="0" t="s">
-        <v>60</v>
+      <c r="G22" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I22" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I22" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J22" s="13"/>
-      <c r="K22" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="0" t="s">
-        <v>63</v>
+      <c r="K22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2567,33 +2645,36 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F23" s="13"/>
-      <c r="G23" s="0" t="s">
-        <v>60</v>
+      <c r="G23" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="I23" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="J23" s="13"/>
-      <c r="K23" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="0" t="s">
-        <v>63</v>
+      <c r="K23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2601,763 +2682,879 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="D25" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" s="20" t="s">
+      <c r="E25" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="0" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="n">
+      <c r="I25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="B25" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I25" s="20" t="n">
+      <c r="L25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M25" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M26" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M27" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M28" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M29" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M33" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M34" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M36" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M37" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K38" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M38" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M39" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M40" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K41" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M41" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M42" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M43" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" s="27" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="J44" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="K44" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L44" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="M44" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M45" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="13"/>
-      <c r="K25" s="21" t="n">
+      <c r="K46" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="L25" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="13" t="s">
+      <c r="L46" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="M46" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J26" s="13"/>
-      <c r="K26" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J27" s="13"/>
-      <c r="K27" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I28" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J28" s="13"/>
-      <c r="K28" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J29" s="13"/>
-      <c r="K29" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I30" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J30" s="13"/>
-      <c r="K30" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J31" s="13"/>
-      <c r="K31" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J32" s="13"/>
-      <c r="K32" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I33" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J33" s="13"/>
-      <c r="K33" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J34" s="13"/>
-      <c r="K34" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I35" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K35" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I36" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K36" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G37" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I37" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K37" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I38" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K38" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K39" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I40" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K40" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I41" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K41" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B42" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I42" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K42" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G43" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I43" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" s="29" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="25" t="n">
-        <v>19</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H44" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I44" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="J44" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="K44" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L44" s="29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G45" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I45" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="K45" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B46" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G46" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L46" s="0" t="s">
-        <v>87</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M3" r:id="rId2" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M4" r:id="rId3" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M5" r:id="rId4" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M6" r:id="rId5" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M7" r:id="rId6" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M8" r:id="rId7" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M9" r:id="rId8" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M10" r:id="rId9" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M11" r:id="rId10" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M12" r:id="rId11" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M13" r:id="rId12" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M14" r:id="rId13" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M15" r:id="rId14" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M16" r:id="rId15" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M17" r:id="rId16" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M18" r:id="rId17" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M19" r:id="rId18" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M20" r:id="rId19" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M21" r:id="rId20" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M22" r:id="rId21" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M23" r:id="rId22" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M24" r:id="rId23" display="javierulloafierro@gmail.com"/>
+    <hyperlink ref="M25" r:id="rId24" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M26" r:id="rId25" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M27" r:id="rId26" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M28" r:id="rId27" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M29" r:id="rId28" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M30" r:id="rId29" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M31" r:id="rId30" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M32" r:id="rId31" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M33" r:id="rId32" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M34" r:id="rId33" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M35" r:id="rId34" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M36" r:id="rId35" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M37" r:id="rId36" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M38" r:id="rId37" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M39" r:id="rId38" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M40" r:id="rId39" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M41" r:id="rId40" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M42" r:id="rId41" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M43" r:id="rId42" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M44" r:id="rId43" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M45" r:id="rId44" display="fierrovergararosaelizabeth@gmail.com"/>
+    <hyperlink ref="M46" r:id="rId45" display="fierrovergararosaelizabeth@gmail.com"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
